--- a/input/Nhân viên_20220128091107.xlsx
+++ b/input/Nhân viên_20220128091107.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="20220128" sheetId="1" r:id="rId1"/>
+    <sheet name="20220209" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4476" uniqueCount="1606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4559" uniqueCount="1630">
   <si>
     <t>Nhân viên</t>
   </si>
@@ -2536,6 +2536,18 @@
     <t>Phạm Thị Vân Hà</t>
   </si>
   <si>
+    <t>A1807</t>
+  </si>
+  <si>
+    <t>Đỗ Hoài Giao</t>
+  </si>
+  <si>
+    <t>It</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
     <t>A1809</t>
   </si>
   <si>
@@ -2626,6 +2638,12 @@
     <t>CÔNG NHÂN XỬ LÝ PHÔI</t>
   </si>
   <si>
+    <t>A1828</t>
+  </si>
+  <si>
+    <t>Lý Huỳnh Như</t>
+  </si>
+  <si>
     <t>A1833</t>
   </si>
   <si>
@@ -2719,6 +2737,12 @@
     <t>2021-03-12</t>
   </si>
   <si>
+    <t>A1856</t>
+  </si>
+  <si>
+    <t>Trần Quốc Vũ</t>
+  </si>
+  <si>
     <t>A1858</t>
   </si>
   <si>
@@ -3160,6 +3184,15 @@
     <t>Bùi Thị Thúy Liễu</t>
   </si>
   <si>
+    <t>A1980</t>
+  </si>
+  <si>
+    <t>Võ Hữu Lễ</t>
+  </si>
+  <si>
+    <t>2021-06-01</t>
+  </si>
+  <si>
     <t>A1981</t>
   </si>
   <si>
@@ -3310,9 +3343,6 @@
     <t>Phan Mạnh Đình</t>
   </si>
   <si>
-    <t>2021-06-01</t>
-  </si>
-  <si>
     <t>A2023</t>
   </si>
   <si>
@@ -3382,6 +3412,12 @@
     <t>2021-06-17</t>
   </si>
   <si>
+    <t>A2046</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Dương</t>
+  </si>
+  <si>
     <t>A2047</t>
   </si>
   <si>
@@ -3451,6 +3487,12 @@
     <t>Trịnh Thị Kim Thúy</t>
   </si>
   <si>
+    <t>A2061</t>
+  </si>
+  <si>
+    <t>Bùi Minh Nhàn</t>
+  </si>
+  <si>
     <t>A2062</t>
   </si>
   <si>
@@ -3475,9 +3517,6 @@
     <t>Triệu Quang Ngọc</t>
   </si>
   <si>
-    <t>It</t>
-  </si>
-  <si>
     <t>NHÂN VIÊN IT</t>
   </si>
   <si>
@@ -3502,6 +3541,12 @@
     <t>Lê Thị Phương Châu</t>
   </si>
   <si>
+    <t>A2069</t>
+  </si>
+  <si>
+    <t>Nguyễn Phước Trung</t>
+  </si>
+  <si>
     <t>A2070</t>
   </si>
   <si>
@@ -3517,6 +3562,12 @@
     <t>2021-11-04</t>
   </si>
   <si>
+    <t>A2072</t>
+  </si>
+  <si>
+    <t>Nguyễn Duy Khôi</t>
+  </si>
+  <si>
     <t>A2074</t>
   </si>
   <si>
@@ -3730,6 +3781,15 @@
     <t>Từ Chí Linh</t>
   </si>
   <si>
+    <t>A2111</t>
+  </si>
+  <si>
+    <t>Trương Nhựt Duy</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>A2112</t>
   </si>
   <si>
@@ -3866,6 +3926,18 @@
   </si>
   <si>
     <t>Nguyễn Trường Duy</t>
+  </si>
+  <si>
+    <t>A2139</t>
+  </si>
+  <si>
+    <t>Phạm Thị Hồng Trang</t>
+  </si>
+  <si>
+    <t>A2140</t>
+  </si>
+  <si>
+    <t>Phạm Thị Hồng Gấm</t>
   </si>
   <si>
     <t>A2141</t>
@@ -5211,7 +5283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I561"/>
+  <dimension ref="A1:I572"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -5227,7 +5299,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1605</v>
+        <v>1629</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12606,18 +12678,16 @@
       <c r="B275" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="C275" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="C275" s="3"/>
       <c r="D275" s="3" t="s">
-        <v>223</v>
+        <v>842</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>379</v>
+        <v>503</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H275" s="3" t="s">
         <v>16</v>
@@ -12628,23 +12698,23 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>99</v>
+        <v>223</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>123</v>
+        <v>379</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>16</v>
@@ -12655,10 +12725,10 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" s="3" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>24</v>
@@ -12682,10 +12752,10 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" s="3" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>24</v>
@@ -12709,19 +12779,19 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" s="3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -12736,23 +12806,23 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
-        <v>853</v>
+        <v>831</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>16</v>
@@ -12763,23 +12833,23 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>16</v>
@@ -12790,10 +12860,10 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>24</v>
@@ -12806,7 +12876,7 @@
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>16</v>
@@ -12817,10 +12887,10 @@
     </row>
     <row r="283" spans="1:9">
       <c r="A283" s="3" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>24</v>
@@ -12833,7 +12903,7 @@
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>16</v>
@@ -12844,10 +12914,10 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>24</v>
@@ -12860,7 +12930,7 @@
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>16</v>
@@ -12871,23 +12941,23 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" s="3" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>511</v>
+        <v>866</v>
       </c>
       <c r="C285" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>347</v>
+        <v>99</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>348</v>
+        <v>123</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>16</v>
@@ -12898,23 +12968,23 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" s="3" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>865</v>
+        <v>511</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>223</v>
+        <v>347</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>16</v>
@@ -12925,23 +12995,23 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C287" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>869</v>
+        <v>379</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>16</v>
@@ -12952,10 +13022,10 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>24</v>
@@ -12964,11 +13034,11 @@
         <v>53</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>16</v>
@@ -12979,23 +13049,23 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>869</v>
+        <v>123</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
-        <v>866</v>
+        <v>834</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>16</v>
@@ -13006,23 +13076,23 @@
     </row>
     <row r="290" spans="1:9">
       <c r="A290" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>347</v>
+        <v>53</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>348</v>
+        <v>873</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>16</v>
@@ -13033,23 +13103,23 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>123</v>
+        <v>873</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>16</v>
@@ -13060,23 +13130,23 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C292" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>34</v>
+        <v>347</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>66</v>
+        <v>348</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>16</v>
@@ -13087,10 +13157,10 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C293" s="3" t="s">
         <v>24</v>
@@ -13103,7 +13173,7 @@
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>16</v>
@@ -13114,23 +13184,23 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>684</v>
+        <v>66</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
-        <v>837</v>
+        <v>882</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>16</v>
@@ -13141,10 +13211,10 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>24</v>
@@ -13157,7 +13227,7 @@
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
-        <v>837</v>
+        <v>882</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>16</v>
@@ -13168,23 +13238,23 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>123</v>
+        <v>684</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
-        <v>876</v>
+        <v>837</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>16</v>
@@ -13195,23 +13265,23 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>422</v>
+        <v>123</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
-        <v>891</v>
+        <v>837</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>16</v>
@@ -13222,10 +13292,10 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>24</v>
@@ -13238,7 +13308,7 @@
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>16</v>
@@ -13255,17 +13325,17 @@
         <v>896</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>897</v>
+        <v>422</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>16</v>
@@ -13312,14 +13382,14 @@
         <v>24</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>123</v>
+        <v>903</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>16</v>
@@ -13330,23 +13400,23 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E302" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="H302" s="3" t="s">
         <v>16</v>
@@ -13357,23 +13427,23 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>907</v>
+        <v>123</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="H303" s="3" t="s">
         <v>16</v>
@@ -13393,14 +13463,14 @@
         <v>24</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="H304" s="3" t="s">
         <v>16</v>
@@ -13411,23 +13481,23 @@
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="B305" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="B305" s="3" t="s">
-        <v>913</v>
-      </c>
       <c r="C305" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="H305" s="3" t="s">
         <v>16</v>
@@ -13438,23 +13508,23 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E306" s="3" t="s">
         <v>915</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="C306" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E306" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H306" s="3" t="s">
         <v>16</v>
@@ -13465,23 +13535,23 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="B307" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="B307" s="3" t="s">
-        <v>919</v>
-      </c>
       <c r="C307" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="H307" s="3" t="s">
         <v>16</v>
@@ -13501,10 +13571,10 @@
         <v>24</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>897</v>
+        <v>123</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -13535,7 +13605,7 @@
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="H309" s="3" t="s">
         <v>16</v>
@@ -13546,10 +13616,10 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>24</v>
@@ -13562,7 +13632,7 @@
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="H310" s="3" t="s">
         <v>16</v>
@@ -13573,23 +13643,23 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="3" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>542</v>
+        <v>154</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>49</v>
+        <v>903</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="H311" s="3" t="s">
         <v>16</v>
@@ -13600,10 +13670,10 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>24</v>
@@ -13616,7 +13686,7 @@
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="H312" s="3" t="s">
         <v>16</v>
@@ -13627,23 +13697,23 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>425</v>
+        <v>123</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
-        <v>933</v>
+        <v>906</v>
       </c>
       <c r="H313" s="3" t="s">
         <v>16</v>
@@ -13654,23 +13724,23 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>223</v>
+        <v>542</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>379</v>
+        <v>49</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="H314" s="3" t="s">
         <v>16</v>
@@ -13690,14 +13760,14 @@
         <v>24</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>820</v>
+        <v>99</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>821</v>
+        <v>123</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
-        <v>939</v>
+        <v>906</v>
       </c>
       <c r="H315" s="3" t="s">
         <v>16</v>
@@ -13708,23 +13778,23 @@
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="B316" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="B316" s="3" t="s">
-        <v>941</v>
-      </c>
       <c r="C316" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H316" s="3" t="s">
         <v>16</v>
@@ -13735,23 +13805,23 @@
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="B317" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="B317" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="C317" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>39</v>
+        <v>223</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="H317" s="3" t="s">
         <v>16</v>
@@ -13762,23 +13832,23 @@
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>39</v>
+        <v>820</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>177</v>
+        <v>821</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="H318" s="3" t="s">
         <v>16</v>
@@ -13789,23 +13859,23 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>223</v>
+        <v>70</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>379</v>
+        <v>422</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="H319" s="3" t="s">
         <v>16</v>
@@ -13816,23 +13886,23 @@
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="3" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>949</v>
+        <v>187</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>542</v>
+        <v>39</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>66</v>
+        <v>390</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="H320" s="3" t="s">
         <v>16</v>
@@ -13843,10 +13913,10 @@
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="3" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>24</v>
@@ -13859,7 +13929,7 @@
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="H321" s="3" t="s">
         <v>16</v>
@@ -13870,23 +13940,23 @@
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>39</v>
+        <v>223</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>160</v>
+        <v>379</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="H322" s="3" t="s">
         <v>16</v>
@@ -13897,23 +13967,23 @@
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>99</v>
+        <v>542</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="H323" s="3" t="s">
         <v>16</v>
@@ -13924,23 +13994,23 @@
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
       <c r="H324" s="3" t="s">
         <v>16</v>
@@ -13951,23 +14021,23 @@
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>410</v>
+        <v>160</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="H325" s="3" t="s">
         <v>16</v>
@@ -13978,23 +14048,23 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>390</v>
+        <v>123</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="H326" s="3" t="s">
         <v>16</v>
@@ -14005,23 +14075,23 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>878</v>
+        <v>966</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="H327" s="3" t="s">
         <v>16</v>
@@ -14032,23 +14102,23 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>127</v>
+        <v>347</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="H328" s="3" t="s">
         <v>16</v>
@@ -14059,23 +14129,23 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>123</v>
+        <v>390</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
-        <v>967</v>
+        <v>950</v>
       </c>
       <c r="H329" s="3" t="s">
         <v>16</v>
@@ -14086,23 +14156,23 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>971</v>
+        <v>884</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
-        <v>967</v>
+        <v>950</v>
       </c>
       <c r="H330" s="3" t="s">
         <v>16</v>
@@ -14113,23 +14183,23 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C331" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>123</v>
+        <v>360</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
-        <v>936</v>
+        <v>975</v>
       </c>
       <c r="H331" s="3" t="s">
         <v>16</v>
@@ -14140,23 +14210,23 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="3" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C332" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
-        <v>914</v>
+        <v>975</v>
       </c>
       <c r="H332" s="3" t="s">
         <v>16</v>
@@ -14167,23 +14237,23 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C333" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
-        <v>914</v>
+        <v>975</v>
       </c>
       <c r="H333" s="3" t="s">
         <v>16</v>
@@ -14194,23 +14264,23 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="3" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>980</v>
+        <v>123</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
-        <v>981</v>
+        <v>944</v>
       </c>
       <c r="H334" s="3" t="s">
         <v>16</v>
@@ -14230,14 +14300,14 @@
         <v>24</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
-        <v>952</v>
+        <v>922</v>
       </c>
       <c r="H335" s="3" t="s">
         <v>16</v>
@@ -14257,14 +14327,14 @@
         <v>24</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>348</v>
+        <v>66</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
-        <v>986</v>
+        <v>922</v>
       </c>
       <c r="H336" s="3" t="s">
         <v>16</v>
@@ -14275,19 +14345,19 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B337" s="3" t="s">
         <v>987</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>988</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>30</v>
+        <v>988</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -14308,17 +14378,17 @@
         <v>991</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
-        <v>981</v>
+        <v>960</v>
       </c>
       <c r="H338" s="3" t="s">
         <v>16</v>
@@ -14338,14 +14408,14 @@
         <v>24</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>99</v>
+        <v>347</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>104</v>
+        <v>348</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
-        <v>961</v>
+        <v>994</v>
       </c>
       <c r="H339" s="3" t="s">
         <v>16</v>
@@ -14356,23 +14426,23 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="H340" s="3" t="s">
         <v>16</v>
@@ -14383,23 +14453,23 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>497</v>
+        <v>202</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="H341" s="3" t="s">
         <v>16</v>
@@ -14410,23 +14480,23 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C342" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>425</v>
+        <v>104</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
-        <v>1000</v>
+        <v>969</v>
       </c>
       <c r="H342" s="3" t="s">
         <v>16</v>
@@ -14437,23 +14507,23 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C343" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="H343" s="3" t="s">
         <v>16</v>
@@ -14464,23 +14534,23 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="H344" s="3" t="s">
         <v>16</v>
@@ -14491,23 +14561,23 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C345" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>173</v>
+        <v>425</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="H345" s="3" t="s">
         <v>16</v>
@@ -14518,23 +14588,23 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="H346" s="3" t="s">
         <v>16</v>
@@ -14545,23 +14615,23 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="3" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>90</v>
+        <v>425</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="H347" s="3" t="s">
         <v>16</v>
@@ -14572,23 +14642,23 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>25</v>
+        <v>198</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
-        <v>1013</v>
+        <v>989</v>
       </c>
       <c r="H348" s="3" t="s">
         <v>16</v>
@@ -14599,23 +14669,23 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>123</v>
+        <v>390</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="H349" s="3" t="s">
         <v>16</v>
@@ -14626,23 +14696,23 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C350" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>684</v>
+        <v>90</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="H350" s="3" t="s">
         <v>16</v>
@@ -14653,23 +14723,23 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C351" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
-        <v>981</v>
+        <v>1021</v>
       </c>
       <c r="H351" s="3" t="s">
         <v>16</v>
@@ -14680,10 +14750,10 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="3" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>24</v>
@@ -14696,7 +14766,7 @@
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="H352" s="3" t="s">
         <v>16</v>
@@ -14707,23 +14777,23 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1024</v>
+        <v>39</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1025</v>
+        <v>684</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
-        <v>936</v>
+        <v>989</v>
       </c>
       <c r="H353" s="3" t="s">
         <v>16</v>
@@ -14750,7 +14820,7 @@
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
-        <v>936</v>
+        <v>989</v>
       </c>
       <c r="H354" s="3" t="s">
         <v>16</v>
@@ -14767,17 +14837,17 @@
         <v>1029</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>691</v>
+        <v>99</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1030</v>
+        <v>123</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
-        <v>1031</v>
+        <v>989</v>
       </c>
       <c r="H355" s="3" t="s">
         <v>16</v>
@@ -14788,23 +14858,23 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D356" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="B356" s="3" t="s">
+      <c r="E356" s="3" t="s">
         <v>1033</v>
-      </c>
-      <c r="C356" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D356" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E356" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="H356" s="3" t="s">
         <v>16</v>
@@ -14824,14 +14894,14 @@
         <v>24</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>390</v>
+        <v>123</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
-        <v>1036</v>
+        <v>944</v>
       </c>
       <c r="H357" s="3" t="s">
         <v>16</v>
@@ -14842,19 +14912,19 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B358" s="3" t="s">
         <v>1037</v>
       </c>
-      <c r="B358" s="3" t="s">
+      <c r="C358" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="E358" s="3" t="s">
         <v>1038</v>
-      </c>
-      <c r="C358" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D358" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E358" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -14878,14 +14948,14 @@
         <v>24</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>49</v>
+        <v>390</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
-        <v>1036</v>
+        <v>944</v>
       </c>
       <c r="H359" s="3" t="s">
         <v>16</v>
@@ -14902,17 +14972,17 @@
         <v>1043</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>289</v>
+        <v>39</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1044</v>
+        <v>390</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H360" s="3" t="s">
         <v>16</v>
@@ -14923,23 +14993,23 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B361" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="B361" s="3" t="s">
-        <v>1047</v>
-      </c>
       <c r="C361" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>202</v>
+        <v>49</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="H361" s="3" t="s">
         <v>16</v>
@@ -14956,17 +15026,17 @@
         <v>1049</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>367</v>
+        <v>49</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H362" s="3" t="s">
         <v>16</v>
@@ -14983,17 +15053,17 @@
         <v>1051</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>66</v>
+        <v>1052</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H363" s="3" t="s">
         <v>16</v>
@@ -15004,10 +15074,10 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="3" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>12</v>
@@ -15016,11 +15086,11 @@
         <v>201</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>710</v>
+        <v>202</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>16</v>
@@ -15031,23 +15101,23 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="3" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>360</v>
+        <v>220</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="H365" s="3" t="s">
         <v>16</v>
@@ -15058,23 +15128,23 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="3" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>154</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>897</v>
+        <v>367</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="H366" s="3" t="s">
         <v>16</v>
@@ -15085,23 +15155,23 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>414</v>
+        <v>25</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1061</v>
+        <v>66</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H367" s="3" t="s">
         <v>16</v>
@@ -15112,23 +15182,23 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="3" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>618</v>
+        <v>1065</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>425</v>
+        <v>710</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
       <c r="H368" s="3" t="s">
         <v>16</v>
@@ -15139,23 +15209,23 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="3" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1067</v>
+        <v>360</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
       <c r="H369" s="3" t="s">
         <v>16</v>
@@ -15175,14 +15245,14 @@
         <v>24</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>116</v>
+        <v>903</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
-        <v>1070</v>
+        <v>1053</v>
       </c>
       <c r="H370" s="3" t="s">
         <v>16</v>
@@ -15193,23 +15263,23 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B371" s="3" t="s">
         <v>1071</v>
       </c>
-      <c r="B371" s="3" t="s">
+      <c r="C371" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D371" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E371" s="3" t="s">
         <v>1072</v>
-      </c>
-      <c r="C371" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D371" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E371" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
       <c r="H371" s="3" t="s">
         <v>16</v>
@@ -15220,23 +15290,23 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="3" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>1074</v>
+        <v>618</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>16</v>
@@ -15247,23 +15317,23 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="3" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>154</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>897</v>
+        <v>1078</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="H373" s="3" t="s">
         <v>16</v>
@@ -15274,23 +15344,23 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="H374" s="3" t="s">
         <v>16</v>
@@ -15301,23 +15371,23 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>897</v>
+        <v>184</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="H375" s="3" t="s">
         <v>16</v>
@@ -15328,10 +15398,10 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>24</v>
@@ -15340,11 +15410,11 @@
         <v>99</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="H376" s="3" t="s">
         <v>16</v>
@@ -15355,23 +15425,23 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C377" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>503</v>
+        <v>903</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
-        <v>1086</v>
+        <v>1075</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>16</v>
@@ -15382,19 +15452,19 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1089</v>
+        <v>66</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -15418,14 +15488,14 @@
         <v>24</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>542</v>
+        <v>154</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>35</v>
+        <v>903</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="H379" s="3" t="s">
         <v>16</v>
@@ -15448,11 +15518,11 @@
         <v>99</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>325</v>
+        <v>123</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
-        <v>1095</v>
+        <v>1081</v>
       </c>
       <c r="H380" s="3" t="s">
         <v>16</v>
@@ -15463,23 +15533,23 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B381" s="3" t="s">
         <v>1096</v>
       </c>
-      <c r="B381" s="3" t="s">
-        <v>1097</v>
-      </c>
       <c r="C381" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>300</v>
+        <v>503</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H381" s="3" t="s">
         <v>16</v>
@@ -15490,19 +15560,19 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B382" s="3" t="s">
         <v>1099</v>
-      </c>
-      <c r="B382" s="3" t="s">
-        <v>1100</v>
       </c>
       <c r="C382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>267</v>
+        <v>1100</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -15526,14 +15596,14 @@
         <v>24</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>112</v>
+        <v>542</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>503</v>
+        <v>35</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
-        <v>1104</v>
+        <v>1081</v>
       </c>
       <c r="H383" s="3" t="s">
         <v>16</v>
@@ -15544,10 +15614,10 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B384" s="3" t="s">
         <v>1105</v>
-      </c>
-      <c r="B384" s="3" t="s">
-        <v>1106</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>24</v>
@@ -15556,11 +15626,11 @@
         <v>99</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="H384" s="3" t="s">
         <v>16</v>
@@ -15580,14 +15650,14 @@
         <v>12</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>394</v>
+        <v>300</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
-        <v>1109</v>
+        <v>1058</v>
       </c>
       <c r="H385" s="3" t="s">
         <v>16</v>
@@ -15598,23 +15668,23 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B386" s="3" t="s">
         <v>1110</v>
-      </c>
-      <c r="B386" s="3" t="s">
-        <v>1111</v>
       </c>
       <c r="C386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>289</v>
+        <v>154</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H386" s="3" t="s">
         <v>16</v>
@@ -15625,23 +15695,23 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B387" s="3" t="s">
         <v>1113</v>
       </c>
-      <c r="B387" s="3" t="s">
-        <v>1114</v>
-      </c>
       <c r="C387" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>360</v>
+        <v>503</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="H387" s="3" t="s">
         <v>16</v>
@@ -15661,14 +15731,14 @@
         <v>24</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>267</v>
+        <v>123</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
-        <v>1101</v>
+        <v>1058</v>
       </c>
       <c r="H388" s="3" t="s">
         <v>16</v>
@@ -15682,20 +15752,20 @@
         <v>1117</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>243</v>
+        <v>1118</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>198</v>
+        <v>289</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>108</v>
+        <v>394</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H389" s="3" t="s">
         <v>16</v>
@@ -15706,23 +15776,23 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="3" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>66</v>
+        <v>290</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H390" s="3" t="s">
         <v>16</v>
@@ -15733,23 +15803,23 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="3" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C391" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>347</v>
+        <v>127</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="H391" s="3" t="s">
         <v>16</v>
@@ -15760,23 +15830,23 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="3" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C392" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>66</v>
+        <v>267</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
-        <v>1126</v>
+        <v>1111</v>
       </c>
       <c r="H392" s="3" t="s">
         <v>16</v>
@@ -15790,20 +15860,20 @@
         <v>1127</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>1128</v>
+        <v>243</v>
       </c>
       <c r="C393" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>347</v>
+        <v>198</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H393" s="3" t="s">
         <v>16</v>
@@ -15814,23 +15884,23 @@
     </row>
     <row r="394" spans="1:9">
       <c r="A394" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B394" s="3" t="s">
         <v>1130</v>
       </c>
-      <c r="B394" s="3" t="s">
-        <v>1131</v>
-      </c>
       <c r="C394" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H394" s="3" t="s">
         <v>16</v>
@@ -15841,23 +15911,21 @@
     </row>
     <row r="395" spans="1:9">
       <c r="A395" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B395" s="3" t="s">
         <v>1133</v>
       </c>
-      <c r="B395" s="3" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C395" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="C395" s="3"/>
       <c r="D395" s="3" t="s">
-        <v>691</v>
+        <v>188</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
-        <v>1135</v>
+        <v>843</v>
       </c>
       <c r="H395" s="3" t="s">
         <v>16</v>
@@ -15868,23 +15936,23 @@
     </row>
     <row r="396" spans="1:9">
       <c r="A396" s="3" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C396" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>44</v>
+        <v>347</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>66</v>
+        <v>348</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
-        <v>1138</v>
+        <v>1111</v>
       </c>
       <c r="H396" s="3" t="s">
         <v>16</v>
@@ -15895,23 +15963,23 @@
     </row>
     <row r="397" spans="1:9">
       <c r="A397" s="3" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="C397" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>347</v>
+        <v>44</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>410</v>
+        <v>66</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="H397" s="3" t="s">
         <v>16</v>
@@ -15922,23 +15990,23 @@
     </row>
     <row r="398" spans="1:9">
       <c r="A398" s="3" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>414</v>
+        <v>347</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1061</v>
+        <v>410</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
-        <v>1062</v>
+        <v>1141</v>
       </c>
       <c r="H398" s="3" t="s">
         <v>16</v>
@@ -15949,23 +16017,23 @@
     </row>
     <row r="399" spans="1:9">
       <c r="A399" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B399" s="3" t="s">
         <v>1143</v>
       </c>
-      <c r="B399" s="3" t="s">
-        <v>1144</v>
-      </c>
       <c r="C399" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>201</v>
+        <v>89</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>202</v>
+        <v>90</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
-        <v>1062</v>
+        <v>1144</v>
       </c>
       <c r="H399" s="3" t="s">
         <v>16</v>
@@ -15985,14 +16053,14 @@
         <v>24</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>154</v>
+        <v>691</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
-        <v>1062</v>
+        <v>1147</v>
       </c>
       <c r="H400" s="3" t="s">
         <v>16</v>
@@ -16003,23 +16071,23 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401" s="3" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C401" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
-        <v>1062</v>
+        <v>1150</v>
       </c>
       <c r="H401" s="3" t="s">
         <v>16</v>
@@ -16030,23 +16098,23 @@
     </row>
     <row r="402" spans="1:9">
       <c r="A402" s="3" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C402" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>89</v>
+        <v>347</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>90</v>
+        <v>410</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
-        <v>1062</v>
+        <v>1141</v>
       </c>
       <c r="H402" s="3" t="s">
         <v>16</v>
@@ -16057,23 +16125,23 @@
     </row>
     <row r="403" spans="1:9">
       <c r="A403" s="3" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1153</v>
+        <v>414</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1154</v>
+        <v>1072</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
-        <v>1155</v>
+        <v>1073</v>
       </c>
       <c r="H403" s="3" t="s">
         <v>16</v>
@@ -16084,23 +16152,23 @@
     </row>
     <row r="404" spans="1:9">
       <c r="A404" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B404" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="B404" s="3" t="s">
-        <v>1157</v>
-      </c>
       <c r="C404" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>89</v>
+        <v>201</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
-        <v>1155</v>
+        <v>1073</v>
       </c>
       <c r="H404" s="3" t="s">
         <v>16</v>
@@ -16111,23 +16179,21 @@
     </row>
     <row r="405" spans="1:9">
       <c r="A405" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B405" s="3" t="s">
         <v>1158</v>
       </c>
-      <c r="B405" s="3" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C405" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="C405" s="3"/>
       <c r="D405" s="3" t="s">
-        <v>89</v>
+        <v>691</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>90</v>
+        <v>503</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
-        <v>1155</v>
+        <v>843</v>
       </c>
       <c r="H405" s="3" t="s">
         <v>16</v>
@@ -16138,23 +16204,23 @@
     </row>
     <row r="406" spans="1:9">
       <c r="A406" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B406" s="3" t="s">
         <v>1160</v>
       </c>
-      <c r="B406" s="3" t="s">
-        <v>1161</v>
-      </c>
       <c r="C406" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>90</v>
+        <v>425</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
-        <v>1155</v>
+        <v>1073</v>
       </c>
       <c r="H406" s="3" t="s">
         <v>16</v>
@@ -16165,10 +16231,10 @@
     </row>
     <row r="407" spans="1:9">
       <c r="A407" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B407" s="3" t="s">
         <v>1162</v>
-      </c>
-      <c r="B407" s="3" t="s">
-        <v>1163</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>24</v>
@@ -16181,7 +16247,7 @@
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
-        <v>1155</v>
+        <v>1073</v>
       </c>
       <c r="H407" s="3" t="s">
         <v>16</v>
@@ -16192,23 +16258,23 @@
     </row>
     <row r="408" spans="1:9">
       <c r="A408" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B408" s="3" t="s">
         <v>1164</v>
       </c>
-      <c r="B408" s="3" t="s">
-        <v>1165</v>
-      </c>
       <c r="C408" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1153</v>
+        <v>89</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1154</v>
+        <v>90</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
-        <v>1166</v>
+        <v>1073</v>
       </c>
       <c r="H408" s="3" t="s">
         <v>16</v>
@@ -16219,23 +16285,23 @@
     </row>
     <row r="409" spans="1:9">
       <c r="A409" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B409" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C409" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D409" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="E409" s="3" t="s">
         <v>1167</v>
-      </c>
-      <c r="B409" s="3" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D409" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E409" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H409" s="3" t="s">
         <v>16</v>
@@ -16246,23 +16312,23 @@
     </row>
     <row r="410" spans="1:9">
       <c r="A410" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B410" s="3" t="s">
         <v>1170</v>
       </c>
-      <c r="B410" s="3" t="s">
-        <v>1171</v>
-      </c>
       <c r="C410" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>503</v>
+        <v>90</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="H410" s="3" t="s">
         <v>16</v>
@@ -16273,10 +16339,10 @@
     </row>
     <row r="411" spans="1:9">
       <c r="A411" s="3" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>24</v>
@@ -16289,7 +16355,7 @@
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="H411" s="3" t="s">
         <v>16</v>
@@ -16300,23 +16366,23 @@
     </row>
     <row r="412" spans="1:9">
       <c r="A412" s="3" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>422</v>
+        <v>90</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="H412" s="3" t="s">
         <v>16</v>
@@ -16327,23 +16393,21 @@
     </row>
     <row r="413" spans="1:9">
       <c r="A413" s="3" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C413" s="3" t="s">
-        <v>24</v>
-      </c>
+        <v>1176</v>
+      </c>
+      <c r="C413" s="3"/>
       <c r="D413" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>425</v>
+        <v>503</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
-        <v>1178</v>
+        <v>843</v>
       </c>
       <c r="H413" s="3" t="s">
         <v>16</v>
@@ -16354,23 +16418,23 @@
     </row>
     <row r="414" spans="1:9">
       <c r="A414" s="3" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="H414" s="3" t="s">
         <v>16</v>
@@ -16381,23 +16445,23 @@
     </row>
     <row r="415" spans="1:9">
       <c r="A415" s="3" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>39</v>
+        <v>842</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>177</v>
+        <v>1167</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="H415" s="3" t="s">
         <v>16</v>
@@ -16408,23 +16472,21 @@
     </row>
     <row r="416" spans="1:9">
       <c r="A416" s="3" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C416" s="3" t="s">
-        <v>24</v>
-      </c>
+        <v>1183</v>
+      </c>
+      <c r="C416" s="3"/>
       <c r="D416" s="3" t="s">
-        <v>89</v>
+        <v>188</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>90</v>
+        <v>503</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
-        <v>1187</v>
+        <v>843</v>
       </c>
       <c r="H416" s="3" t="s">
         <v>16</v>
@@ -16435,23 +16497,23 @@
     </row>
     <row r="417" spans="1:9">
       <c r="A417" s="3" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="H417" s="3" t="s">
         <v>16</v>
@@ -16462,10 +16524,10 @@
     </row>
     <row r="418" spans="1:9">
       <c r="A418" s="3" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>24</v>
@@ -16478,7 +16540,7 @@
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="H418" s="3" t="s">
         <v>16</v>
@@ -16489,23 +16551,23 @@
     </row>
     <row r="419" spans="1:9">
       <c r="A419" s="3" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H419" s="3" t="s">
         <v>16</v>
@@ -16516,23 +16578,23 @@
     </row>
     <row r="420" spans="1:9">
       <c r="A420" s="3" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>66</v>
+        <v>422</v>
       </c>
       <c r="F420" s="3"/>
       <c r="G420" s="3" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="H420" s="3" t="s">
         <v>16</v>
@@ -16543,23 +16605,23 @@
     </row>
     <row r="421" spans="1:9">
       <c r="A421" s="3" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>66</v>
+        <v>425</v>
       </c>
       <c r="F421" s="3"/>
       <c r="G421" s="3" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="H421" s="3" t="s">
         <v>16</v>
@@ -16570,23 +16632,23 @@
     </row>
     <row r="422" spans="1:9">
       <c r="A422" s="3" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="F422" s="3"/>
       <c r="G422" s="3" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="H422" s="3" t="s">
         <v>16</v>
@@ -16597,10 +16659,10 @@
     </row>
     <row r="423" spans="1:9">
       <c r="A423" s="3" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>24</v>
@@ -16609,11 +16671,11 @@
         <v>39</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="F423" s="3"/>
       <c r="G423" s="3" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="H423" s="3" t="s">
         <v>16</v>
@@ -16624,23 +16686,23 @@
     </row>
     <row r="424" spans="1:9">
       <c r="A424" s="3" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="C424" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>503</v>
+        <v>90</v>
       </c>
       <c r="F424" s="3"/>
       <c r="G424" s="3" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="H424" s="3" t="s">
         <v>16</v>
@@ -16651,23 +16713,23 @@
     </row>
     <row r="425" spans="1:9">
       <c r="A425" s="3" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="H425" s="3" t="s">
         <v>16</v>
@@ -16678,19 +16740,19 @@
     </row>
     <row r="426" spans="1:9">
       <c r="A426" s="3" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -16705,23 +16767,23 @@
     </row>
     <row r="427" spans="1:9">
       <c r="A427" s="3" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>223</v>
+        <v>99</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>497</v>
+        <v>123</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="H427" s="3" t="s">
         <v>16</v>
@@ -16732,23 +16794,23 @@
     </row>
     <row r="428" spans="1:9">
       <c r="A428" s="3" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C428" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>684</v>
+        <v>66</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="H428" s="3" t="s">
         <v>16</v>
@@ -16759,23 +16821,23 @@
     </row>
     <row r="429" spans="1:9">
       <c r="A429" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B429" s="3" t="s">
         <v>1217</v>
       </c>
-      <c r="B429" s="3" t="s">
-        <v>1218</v>
-      </c>
       <c r="C429" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="H429" s="3" t="s">
         <v>16</v>
@@ -16786,23 +16848,23 @@
     </row>
     <row r="430" spans="1:9">
       <c r="A430" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B430" s="3" t="s">
         <v>1219</v>
       </c>
-      <c r="B430" s="3" t="s">
-        <v>1220</v>
-      </c>
       <c r="C430" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="H430" s="3" t="s">
         <v>16</v>
@@ -16813,23 +16875,23 @@
     </row>
     <row r="431" spans="1:9">
       <c r="A431" s="3" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1224</v>
+        <v>160</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="H431" s="3" t="s">
         <v>16</v>
@@ -16840,23 +16902,23 @@
     </row>
     <row r="432" spans="1:9">
       <c r="A432" s="3" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1227</v>
+        <v>112</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>90</v>
+        <v>503</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="H432" s="3" t="s">
         <v>16</v>
@@ -16867,23 +16929,23 @@
     </row>
     <row r="433" spans="1:9">
       <c r="A433" s="3" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>820</v>
+        <v>127</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>821</v>
+        <v>360</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="H433" s="3" t="s">
         <v>16</v>
@@ -16894,23 +16956,23 @@
     </row>
     <row r="434" spans="1:9">
       <c r="A434" s="3" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>237</v>
+        <v>520</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
-        <v>1118</v>
+        <v>1227</v>
       </c>
       <c r="H434" s="3" t="s">
         <v>16</v>
@@ -16921,23 +16983,23 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435" s="3" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="C435" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>209</v>
+        <v>497</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
-        <v>1235</v>
+        <v>1224</v>
       </c>
       <c r="H435" s="3" t="s">
         <v>16</v>
@@ -16948,23 +17010,23 @@
     </row>
     <row r="436" spans="1:9">
       <c r="A436" s="3" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="C436" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>223</v>
+        <v>39</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>379</v>
+        <v>684</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
-        <v>1118</v>
+        <v>1207</v>
       </c>
       <c r="H436" s="3" t="s">
         <v>16</v>
@@ -16975,23 +17037,23 @@
     </row>
     <row r="437" spans="1:9">
       <c r="A437" s="3" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>414</v>
+        <v>99</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1061</v>
+        <v>123</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
-        <v>1230</v>
+        <v>1207</v>
       </c>
       <c r="H437" s="3" t="s">
         <v>16</v>
@@ -17002,23 +17064,23 @@
     </row>
     <row r="438" spans="1:9">
       <c r="A438" s="3" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="C438" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>223</v>
+        <v>154</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>379</v>
+        <v>155</v>
       </c>
       <c r="F438" s="3"/>
       <c r="G438" s="3" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="H438" s="3" t="s">
         <v>16</v>
@@ -17029,23 +17091,23 @@
     </row>
     <row r="439" spans="1:9">
       <c r="A439" s="3" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C439" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>367</v>
+        <v>1241</v>
       </c>
       <c r="F439" s="3"/>
       <c r="G439" s="3" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="H439" s="3" t="s">
         <v>16</v>
@@ -17056,23 +17118,23 @@
     </row>
     <row r="440" spans="1:9">
       <c r="A440" s="3" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="C440" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>154</v>
+        <v>1244</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>897</v>
+        <v>90</v>
       </c>
       <c r="F440" s="3"/>
       <c r="G440" s="3" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="H440" s="3" t="s">
         <v>16</v>
@@ -17083,23 +17145,23 @@
     </row>
     <row r="441" spans="1:9">
       <c r="A441" s="3" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C441" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>289</v>
+        <v>820</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>394</v>
+        <v>821</v>
       </c>
       <c r="F441" s="3"/>
       <c r="G441" s="3" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="H441" s="3" t="s">
         <v>16</v>
@@ -17110,23 +17172,23 @@
     </row>
     <row r="442" spans="1:9">
       <c r="A442" s="3" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C442" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>123</v>
+        <v>237</v>
       </c>
       <c r="F442" s="3"/>
       <c r="G442" s="3" t="s">
-        <v>1230</v>
+        <v>1128</v>
       </c>
       <c r="H442" s="3" t="s">
         <v>16</v>
@@ -17137,23 +17199,23 @@
     </row>
     <row r="443" spans="1:9">
       <c r="A443" s="3" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>422</v>
+        <v>209</v>
       </c>
       <c r="F443" s="3"/>
       <c r="G443" s="3" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="H443" s="3" t="s">
         <v>16</v>
@@ -17164,23 +17226,23 @@
     </row>
     <row r="444" spans="1:9">
       <c r="A444" s="3" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>414</v>
+        <v>223</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1061</v>
+        <v>379</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
-        <v>1245</v>
+        <v>1128</v>
       </c>
       <c r="H444" s="3" t="s">
         <v>16</v>
@@ -17191,23 +17253,23 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445" s="3" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>896</v>
+        <v>1256</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>12</v>
+        <v>1257</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>367</v>
+        <v>237</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
-        <v>1259</v>
+        <v>1128</v>
       </c>
       <c r="H445" s="3" t="s">
         <v>16</v>
@@ -17218,23 +17280,23 @@
     </row>
     <row r="446" spans="1:9">
       <c r="A446" s="3" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C446" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>201</v>
+        <v>414</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>202</v>
+        <v>1072</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
-        <v>1262</v>
+        <v>1247</v>
       </c>
       <c r="H446" s="3" t="s">
         <v>16</v>
@@ -17245,19 +17307,19 @@
     </row>
     <row r="447" spans="1:9">
       <c r="A447" s="3" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C447" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>99</v>
+        <v>223</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>123</v>
+        <v>379</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -17272,23 +17334,23 @@
     </row>
     <row r="448" spans="1:9">
       <c r="A448" s="3" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>123</v>
+        <v>367</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="H448" s="3" t="s">
         <v>16</v>
@@ -17299,23 +17361,23 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" s="3" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>61</v>
+        <v>154</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>520</v>
+        <v>903</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
-        <v>1259</v>
+        <v>1247</v>
       </c>
       <c r="H449" s="3" t="s">
         <v>16</v>
@@ -17326,23 +17388,23 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450" s="3" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C450" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1024</v>
+        <v>289</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>241</v>
+        <v>394</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
-        <v>1259</v>
+        <v>1270</v>
       </c>
       <c r="H450" s="3" t="s">
         <v>16</v>
@@ -17353,23 +17415,23 @@
     </row>
     <row r="451" spans="1:9">
       <c r="A451" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B451" s="3" t="s">
         <v>1272</v>
       </c>
-      <c r="B451" s="3" t="s">
-        <v>1273</v>
-      </c>
       <c r="C451" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>425</v>
+        <v>123</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
-        <v>1274</v>
+        <v>1247</v>
       </c>
       <c r="H451" s="3" t="s">
         <v>16</v>
@@ -17380,23 +17442,23 @@
     </row>
     <row r="452" spans="1:9">
       <c r="A452" s="3" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>123</v>
+        <v>422</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="H452" s="3" t="s">
         <v>16</v>
@@ -17407,23 +17469,23 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B453" s="3" t="s">
         <v>1277</v>
       </c>
-      <c r="B453" s="3" t="s">
-        <v>1278</v>
-      </c>
       <c r="C453" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>99</v>
+        <v>414</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>123</v>
+        <v>1072</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="H453" s="3" t="s">
         <v>16</v>
@@ -17434,23 +17496,23 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454" s="3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>1280</v>
+        <v>902</v>
       </c>
       <c r="C454" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>422</v>
+        <v>367</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="H454" s="3" t="s">
         <v>16</v>
@@ -17461,23 +17523,23 @@
     </row>
     <row r="455" spans="1:9">
       <c r="A455" s="3" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>123</v>
+        <v>202</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
-        <v>1259</v>
+        <v>1282</v>
       </c>
       <c r="H455" s="3" t="s">
         <v>16</v>
@@ -17488,23 +17550,23 @@
     </row>
     <row r="456" spans="1:9">
       <c r="A456" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B456" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="B456" s="3" t="s">
-        <v>1285</v>
-      </c>
       <c r="C456" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1286</v>
+        <v>99</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
-        <v>1259</v>
+        <v>1282</v>
       </c>
       <c r="H456" s="3" t="s">
         <v>16</v>
@@ -17515,10 +17577,10 @@
     </row>
     <row r="457" spans="1:9">
       <c r="A457" s="3" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C457" s="3" t="s">
         <v>24</v>
@@ -17531,7 +17593,7 @@
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="H457" s="3" t="s">
         <v>16</v>
@@ -17542,23 +17604,23 @@
     </row>
     <row r="458" spans="1:9">
       <c r="A458" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B458" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="B458" s="3" t="s">
-        <v>1290</v>
-      </c>
       <c r="C458" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>542</v>
+        <v>61</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>57</v>
+        <v>520</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="H458" s="3" t="s">
         <v>16</v>
@@ -17569,23 +17631,23 @@
     </row>
     <row r="459" spans="1:9">
       <c r="A459" s="3" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C459" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>39</v>
+        <v>1032</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>684</v>
+        <v>241</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
-        <v>1294</v>
+        <v>1279</v>
       </c>
       <c r="H459" s="3" t="s">
         <v>16</v>
@@ -17596,19 +17658,19 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460" s="3" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="C460" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>229</v>
+        <v>425</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -17623,10 +17685,10 @@
     </row>
     <row r="461" spans="1:9">
       <c r="A461" s="3" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C461" s="3" t="s">
         <v>24</v>
@@ -17639,7 +17701,7 @@
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
-        <v>1299</v>
+        <v>1287</v>
       </c>
       <c r="H461" s="3" t="s">
         <v>16</v>
@@ -17650,23 +17712,23 @@
     </row>
     <row r="462" spans="1:9">
       <c r="A462" s="3" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C462" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F462" s="3"/>
       <c r="G462" s="3" t="s">
-        <v>1302</v>
+        <v>1287</v>
       </c>
       <c r="H462" s="3" t="s">
         <v>16</v>
@@ -17677,23 +17739,23 @@
     </row>
     <row r="463" spans="1:9">
       <c r="A463" s="3" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="C463" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1305</v>
+        <v>422</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="3" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="H463" s="3" t="s">
         <v>16</v>
@@ -17704,23 +17766,23 @@
     </row>
     <row r="464" spans="1:9">
       <c r="A464" s="3" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="C464" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1309</v>
+        <v>123</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
-        <v>1310</v>
+        <v>1279</v>
       </c>
       <c r="H464" s="3" t="s">
         <v>16</v>
@@ -17731,23 +17793,23 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465" s="3" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>1312</v>
+        <v>1305</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>24</v>
+        <v>1257</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>39</v>
+        <v>1244</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1309</v>
+        <v>123</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
-        <v>1310</v>
+        <v>1279</v>
       </c>
       <c r="H465" s="3" t="s">
         <v>16</v>
@@ -17758,23 +17820,23 @@
     </row>
     <row r="466" spans="1:9">
       <c r="A466" s="3" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>12</v>
+        <v>1257</v>
       </c>
       <c r="D466" s="3" t="s">
-        <v>127</v>
+        <v>1244</v>
       </c>
       <c r="E466" s="3" t="s">
-        <v>1315</v>
+        <v>123</v>
       </c>
       <c r="F466" s="3"/>
       <c r="G466" s="3" t="s">
-        <v>1316</v>
+        <v>1279</v>
       </c>
       <c r="H466" s="3" t="s">
         <v>16</v>
@@ -17785,23 +17847,23 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467" s="3" t="s">
-        <v>1317</v>
+        <v>1308</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>1318</v>
+        <v>1309</v>
       </c>
       <c r="C467" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>25</v>
+        <v>1310</v>
       </c>
       <c r="E467" s="3" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="F467" s="3"/>
       <c r="G467" s="3" t="s">
-        <v>1319</v>
+        <v>1279</v>
       </c>
       <c r="H467" s="3" t="s">
         <v>16</v>
@@ -17812,23 +17874,23 @@
     </row>
     <row r="468" spans="1:9">
       <c r="A468" s="3" t="s">
-        <v>1320</v>
+        <v>1311</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>1321</v>
+        <v>1312</v>
       </c>
       <c r="C468" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="E468" s="3" t="s">
-        <v>253</v>
+        <v>123</v>
       </c>
       <c r="F468" s="3"/>
       <c r="G468" s="3" t="s">
-        <v>1322</v>
+        <v>1301</v>
       </c>
       <c r="H468" s="3" t="s">
         <v>16</v>
@@ -17839,23 +17901,23 @@
     </row>
     <row r="469" spans="1:9">
       <c r="A469" s="3" t="s">
-        <v>1323</v>
+        <v>1313</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>1324</v>
+        <v>1314</v>
       </c>
       <c r="C469" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>89</v>
+        <v>542</v>
       </c>
       <c r="E469" s="3" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F469" s="3"/>
       <c r="G469" s="3" t="s">
-        <v>1325</v>
+        <v>1315</v>
       </c>
       <c r="H469" s="3" t="s">
         <v>16</v>
@@ -17866,23 +17928,23 @@
     </row>
     <row r="470" spans="1:9">
       <c r="A470" s="3" t="s">
-        <v>1326</v>
+        <v>1316</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>1327</v>
+        <v>1317</v>
       </c>
       <c r="C470" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>1328</v>
+        <v>39</v>
       </c>
       <c r="E470" s="3" t="s">
-        <v>869</v>
+        <v>684</v>
       </c>
       <c r="F470" s="3"/>
       <c r="G470" s="3" t="s">
-        <v>1329</v>
+        <v>1318</v>
       </c>
       <c r="H470" s="3" t="s">
         <v>16</v>
@@ -17893,23 +17955,23 @@
     </row>
     <row r="471" spans="1:9">
       <c r="A471" s="3" t="s">
-        <v>1330</v>
+        <v>1319</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>1331</v>
+        <v>1320</v>
       </c>
       <c r="C471" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="E471" s="3" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="F471" s="3"/>
       <c r="G471" s="3" t="s">
-        <v>1332</v>
+        <v>1318</v>
       </c>
       <c r="H471" s="3" t="s">
         <v>16</v>
@@ -17920,23 +17982,23 @@
     </row>
     <row r="472" spans="1:9">
       <c r="A472" s="3" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>1334</v>
+        <v>1322</v>
       </c>
       <c r="C472" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E472" s="3" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="F472" s="3"/>
       <c r="G472" s="3" t="s">
-        <v>1335</v>
+        <v>1323</v>
       </c>
       <c r="H472" s="3" t="s">
         <v>16</v>
@@ -17947,23 +18009,23 @@
     </row>
     <row r="473" spans="1:9">
       <c r="A473" s="3" t="s">
-        <v>1336</v>
+        <v>1324</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>1337</v>
+        <v>1325</v>
       </c>
       <c r="C473" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E473" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F473" s="3"/>
       <c r="G473" s="3" t="s">
-        <v>1338</v>
+        <v>1326</v>
       </c>
       <c r="H473" s="3" t="s">
         <v>16</v>
@@ -17974,23 +18036,23 @@
     </row>
     <row r="474" spans="1:9">
       <c r="A474" s="3" t="s">
-        <v>1339</v>
+        <v>1327</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>1340</v>
+        <v>1328</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>123</v>
+        <v>1329</v>
       </c>
       <c r="F474" s="3"/>
       <c r="G474" s="3" t="s">
-        <v>1341</v>
+        <v>1330</v>
       </c>
       <c r="H474" s="3" t="s">
         <v>16</v>
@@ -18001,23 +18063,23 @@
     </row>
     <row r="475" spans="1:9">
       <c r="A475" s="3" t="s">
-        <v>1342</v>
+        <v>1331</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>1343</v>
+        <v>1332</v>
       </c>
       <c r="C475" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>1344</v>
+        <v>1333</v>
       </c>
       <c r="F475" s="3"/>
       <c r="G475" s="3" t="s">
-        <v>1345</v>
+        <v>1334</v>
       </c>
       <c r="H475" s="3" t="s">
         <v>16</v>
@@ -18028,23 +18090,23 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" s="3" t="s">
-        <v>1346</v>
+        <v>1335</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>1347</v>
+        <v>1336</v>
       </c>
       <c r="C476" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E476" s="3" t="s">
-        <v>104</v>
+        <v>1333</v>
       </c>
       <c r="F476" s="3"/>
       <c r="G476" s="3" t="s">
-        <v>1348</v>
+        <v>1334</v>
       </c>
       <c r="H476" s="3" t="s">
         <v>16</v>
@@ -18055,23 +18117,23 @@
     </row>
     <row r="477" spans="1:9">
       <c r="A477" s="3" t="s">
-        <v>1349</v>
+        <v>1337</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>1350</v>
+        <v>1338</v>
       </c>
       <c r="C477" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="E477" s="3" t="s">
-        <v>104</v>
+        <v>1339</v>
       </c>
       <c r="F477" s="3"/>
       <c r="G477" s="3" t="s">
-        <v>1351</v>
+        <v>1340</v>
       </c>
       <c r="H477" s="3" t="s">
         <v>16</v>
@@ -18082,23 +18144,23 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478" s="3" t="s">
-        <v>1352</v>
+        <v>1341</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>1353</v>
+        <v>1342</v>
       </c>
       <c r="C478" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E478" s="3" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="F478" s="3"/>
       <c r="G478" s="3" t="s">
-        <v>1354</v>
+        <v>1343</v>
       </c>
       <c r="H478" s="3" t="s">
         <v>16</v>
@@ -18109,23 +18171,23 @@
     </row>
     <row r="479" spans="1:9">
       <c r="A479" s="3" t="s">
-        <v>1355</v>
+        <v>1344</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1356</v>
+        <v>1345</v>
       </c>
       <c r="C479" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="E479" s="3" t="s">
-        <v>123</v>
+        <v>253</v>
       </c>
       <c r="F479" s="3"/>
       <c r="G479" s="3" t="s">
-        <v>1357</v>
+        <v>1346</v>
       </c>
       <c r="H479" s="3" t="s">
         <v>16</v>
@@ -18136,23 +18198,23 @@
     </row>
     <row r="480" spans="1:9">
       <c r="A480" s="3" t="s">
-        <v>1358</v>
+        <v>1347</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>1359</v>
+        <v>1348</v>
       </c>
       <c r="C480" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E480" s="3" t="s">
-        <v>343</v>
+        <v>90</v>
       </c>
       <c r="F480" s="3"/>
       <c r="G480" s="3" t="s">
-        <v>1360</v>
+        <v>1349</v>
       </c>
       <c r="H480" s="3" t="s">
         <v>16</v>
@@ -18163,23 +18225,23 @@
     </row>
     <row r="481" spans="1:9">
       <c r="A481" s="3" t="s">
-        <v>1361</v>
+        <v>1350</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>1362</v>
+        <v>1351</v>
       </c>
       <c r="C481" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>99</v>
+        <v>1352</v>
       </c>
       <c r="E481" s="3" t="s">
-        <v>123</v>
+        <v>873</v>
       </c>
       <c r="F481" s="3"/>
       <c r="G481" s="3" t="s">
-        <v>1363</v>
+        <v>1353</v>
       </c>
       <c r="H481" s="3" t="s">
         <v>16</v>
@@ -18190,23 +18252,23 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482" s="3" t="s">
-        <v>1364</v>
+        <v>1354</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>1365</v>
+        <v>1355</v>
       </c>
       <c r="C482" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D482" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E482" s="3" t="s">
-        <v>271</v>
+        <v>35</v>
       </c>
       <c r="F482" s="3"/>
       <c r="G482" s="3" t="s">
-        <v>1366</v>
+        <v>1356</v>
       </c>
       <c r="H482" s="3" t="s">
         <v>16</v>
@@ -18217,23 +18279,23 @@
     </row>
     <row r="483" spans="1:9">
       <c r="A483" s="3" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>1368</v>
+        <v>1358</v>
       </c>
       <c r="C483" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="E483" s="3" t="s">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="F483" s="3"/>
       <c r="G483" s="3" t="s">
-        <v>1369</v>
+        <v>1359</v>
       </c>
       <c r="H483" s="3" t="s">
         <v>16</v>
@@ -18244,23 +18306,23 @@
     </row>
     <row r="484" spans="1:9">
       <c r="A484" s="3" t="s">
-        <v>1370</v>
+        <v>1360</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>1371</v>
+        <v>1361</v>
       </c>
       <c r="C484" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="E484" s="3" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="F484" s="3"/>
       <c r="G484" s="3" t="s">
-        <v>1372</v>
+        <v>1362</v>
       </c>
       <c r="H484" s="3" t="s">
         <v>16</v>
@@ -18271,10 +18333,10 @@
     </row>
     <row r="485" spans="1:9">
       <c r="A485" s="3" t="s">
-        <v>1373</v>
+        <v>1363</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1374</v>
+        <v>1364</v>
       </c>
       <c r="C485" s="3" t="s">
         <v>24</v>
@@ -18283,11 +18345,11 @@
         <v>99</v>
       </c>
       <c r="E485" s="3" t="s">
-        <v>1375</v>
+        <v>123</v>
       </c>
       <c r="F485" s="3"/>
       <c r="G485" s="3" t="s">
-        <v>1376</v>
+        <v>1365</v>
       </c>
       <c r="H485" s="3" t="s">
         <v>16</v>
@@ -18298,23 +18360,23 @@
     </row>
     <row r="486" spans="1:9">
       <c r="A486" s="3" t="s">
-        <v>1377</v>
+        <v>1366</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>1378</v>
+        <v>1367</v>
       </c>
       <c r="C486" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D486" s="3" t="s">
-        <v>39</v>
+        <v>347</v>
       </c>
       <c r="E486" s="3" t="s">
-        <v>343</v>
+        <v>1368</v>
       </c>
       <c r="F486" s="3"/>
       <c r="G486" s="3" t="s">
-        <v>1379</v>
+        <v>1369</v>
       </c>
       <c r="H486" s="3" t="s">
         <v>16</v>
@@ -18325,23 +18387,23 @@
     </row>
     <row r="487" spans="1:9">
       <c r="A487" s="3" t="s">
-        <v>1380</v>
+        <v>1370</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1381</v>
+        <v>1371</v>
       </c>
       <c r="C487" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E487" s="3" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="F487" s="3"/>
       <c r="G487" s="3" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="H487" s="3" t="s">
         <v>16</v>
@@ -18352,10 +18414,10 @@
     </row>
     <row r="488" spans="1:9">
       <c r="A488" s="3" t="s">
-        <v>1382</v>
+        <v>1373</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>1383</v>
+        <v>1374</v>
       </c>
       <c r="C488" s="3" t="s">
         <v>24</v>
@@ -18364,11 +18426,11 @@
         <v>99</v>
       </c>
       <c r="E488" s="3" t="s">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="F488" s="3"/>
       <c r="G488" s="3" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="H488" s="3" t="s">
         <v>16</v>
@@ -18379,10 +18441,10 @@
     </row>
     <row r="489" spans="1:9">
       <c r="A489" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
       <c r="C489" s="3" t="s">
         <v>24</v>
@@ -18395,7 +18457,7 @@
       </c>
       <c r="F489" s="3"/>
       <c r="G489" s="3" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
       <c r="H489" s="3" t="s">
         <v>16</v>
@@ -18406,23 +18468,23 @@
     </row>
     <row r="490" spans="1:9">
       <c r="A490" s="3" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="C490" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E490" s="3" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="F490" s="3"/>
       <c r="G490" s="3" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
       <c r="H490" s="3" t="s">
         <v>16</v>
@@ -18433,23 +18495,23 @@
     </row>
     <row r="491" spans="1:9">
       <c r="A491" s="3" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
       <c r="C491" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>542</v>
+        <v>39</v>
       </c>
       <c r="E491" s="3" t="s">
-        <v>26</v>
+        <v>343</v>
       </c>
       <c r="F491" s="3"/>
       <c r="G491" s="3" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
       <c r="H491" s="3" t="s">
         <v>16</v>
@@ -18460,10 +18522,10 @@
     </row>
     <row r="492" spans="1:9">
       <c r="A492" s="3" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="C492" s="3" t="s">
         <v>24</v>
@@ -18472,11 +18534,11 @@
         <v>99</v>
       </c>
       <c r="E492" s="3" t="s">
-        <v>325</v>
+        <v>123</v>
       </c>
       <c r="F492" s="3"/>
       <c r="G492" s="3" t="s">
-        <v>1357</v>
+        <v>1387</v>
       </c>
       <c r="H492" s="3" t="s">
         <v>16</v>
@@ -18487,23 +18549,23 @@
     </row>
     <row r="493" spans="1:9">
       <c r="A493" s="3" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D493" s="3" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="E493" s="3" t="s">
-        <v>980</v>
+        <v>271</v>
       </c>
       <c r="F493" s="3"/>
       <c r="G493" s="3" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="H493" s="3" t="s">
         <v>16</v>
@@ -18514,23 +18576,23 @@
     </row>
     <row r="494" spans="1:9">
       <c r="A494" s="3" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
       <c r="C494" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E494" s="3" t="s">
-        <v>601</v>
+        <v>173</v>
       </c>
       <c r="F494" s="3"/>
       <c r="G494" s="3" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="H494" s="3" t="s">
         <v>16</v>
@@ -18541,23 +18603,23 @@
     </row>
     <row r="495" spans="1:9">
       <c r="A495" s="3" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="C495" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>542</v>
+        <v>99</v>
       </c>
       <c r="E495" s="3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="F495" s="3"/>
       <c r="G495" s="3" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="H495" s="3" t="s">
         <v>16</v>
@@ -18568,23 +18630,23 @@
     </row>
     <row r="496" spans="1:9">
       <c r="A496" s="3" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="E496" s="3" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="F496" s="3"/>
       <c r="G496" s="3" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="H496" s="3" t="s">
         <v>16</v>
@@ -18595,23 +18657,23 @@
     </row>
     <row r="497" spans="1:9">
       <c r="A497" s="3" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>93</v>
+        <v>1402</v>
       </c>
       <c r="C497" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
       <c r="E497" s="3" t="s">
-        <v>229</v>
+        <v>343</v>
       </c>
       <c r="F497" s="3"/>
       <c r="G497" s="3" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
       <c r="H497" s="3" t="s">
         <v>16</v>
@@ -18622,23 +18684,23 @@
     </row>
     <row r="498" spans="1:9">
       <c r="A498" s="3" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="E498" s="3" t="s">
-        <v>1412</v>
+        <v>66</v>
       </c>
       <c r="F498" s="3"/>
       <c r="G498" s="3" t="s">
-        <v>1413</v>
+        <v>1403</v>
       </c>
       <c r="H498" s="3" t="s">
         <v>16</v>
@@ -18649,23 +18711,23 @@
     </row>
     <row r="499" spans="1:9">
       <c r="A499" s="3" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="C499" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E499" s="3" t="s">
-        <v>1416</v>
+        <v>325</v>
       </c>
       <c r="F499" s="3"/>
       <c r="G499" s="3" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="H499" s="3" t="s">
         <v>16</v>
@@ -18676,23 +18738,23 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500" s="3" t="s">
-        <v>1418</v>
+        <v>1408</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>1419</v>
+        <v>1409</v>
       </c>
       <c r="C500" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>347</v>
+        <v>99</v>
       </c>
       <c r="E500" s="3" t="s">
-        <v>348</v>
+        <v>104</v>
       </c>
       <c r="F500" s="3"/>
       <c r="G500" s="3" t="s">
-        <v>1420</v>
+        <v>1410</v>
       </c>
       <c r="H500" s="3" t="s">
         <v>16</v>
@@ -18703,23 +18765,23 @@
     </row>
     <row r="501" spans="1:9">
       <c r="A501" s="3" t="s">
-        <v>1421</v>
+        <v>1411</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>1422</v>
+        <v>1412</v>
       </c>
       <c r="C501" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E501" s="3" t="s">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="F501" s="3"/>
       <c r="G501" s="3" t="s">
-        <v>1423</v>
+        <v>1413</v>
       </c>
       <c r="H501" s="3" t="s">
         <v>16</v>
@@ -18730,23 +18792,23 @@
     </row>
     <row r="502" spans="1:9">
       <c r="A502" s="3" t="s">
-        <v>1424</v>
+        <v>1414</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>1425</v>
+        <v>1415</v>
       </c>
       <c r="C502" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>259</v>
+        <v>542</v>
       </c>
       <c r="E502" s="3" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="F502" s="3"/>
       <c r="G502" s="3" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="H502" s="3" t="s">
         <v>16</v>
@@ -18757,23 +18819,23 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" s="3" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="C503" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="E503" s="3" t="s">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="F503" s="3"/>
       <c r="G503" s="3" t="s">
-        <v>1429</v>
+        <v>1381</v>
       </c>
       <c r="H503" s="3" t="s">
         <v>16</v>
@@ -18784,23 +18846,23 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" s="3" t="s">
-        <v>1430</v>
+        <v>1419</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>1431</v>
+        <v>1420</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>347</v>
+        <v>154</v>
       </c>
       <c r="E504" s="3" t="s">
-        <v>348</v>
+        <v>988</v>
       </c>
       <c r="F504" s="3"/>
       <c r="G504" s="3" t="s">
-        <v>1432</v>
+        <v>1421</v>
       </c>
       <c r="H504" s="3" t="s">
         <v>16</v>
@@ -18811,23 +18873,23 @@
     </row>
     <row r="505" spans="1:9">
       <c r="A505" s="3" t="s">
-        <v>1433</v>
+        <v>1422</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1434</v>
+        <v>1423</v>
       </c>
       <c r="C505" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>44</v>
+        <v>223</v>
       </c>
       <c r="E505" s="3" t="s">
-        <v>49</v>
+        <v>601</v>
       </c>
       <c r="F505" s="3"/>
       <c r="G505" s="3" t="s">
-        <v>1435</v>
+        <v>1424</v>
       </c>
       <c r="H505" s="3" t="s">
         <v>16</v>
@@ -18838,23 +18900,23 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506" s="3" t="s">
-        <v>1436</v>
+        <v>1425</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>1437</v>
+        <v>1426</v>
       </c>
       <c r="C506" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>99</v>
+        <v>542</v>
       </c>
       <c r="E506" s="3" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="F506" s="3"/>
       <c r="G506" s="3" t="s">
-        <v>1438</v>
+        <v>1427</v>
       </c>
       <c r="H506" s="3" t="s">
         <v>16</v>
@@ -18865,23 +18927,23 @@
     </row>
     <row r="507" spans="1:9">
       <c r="A507" s="3" t="s">
-        <v>1439</v>
+        <v>1428</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>1440</v>
+        <v>1429</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="E507" s="3" t="s">
-        <v>123</v>
+        <v>1430</v>
       </c>
       <c r="F507" s="3"/>
       <c r="G507" s="3" t="s">
-        <v>1441</v>
+        <v>1431</v>
       </c>
       <c r="H507" s="3" t="s">
         <v>16</v>
@@ -18892,23 +18954,23 @@
     </row>
     <row r="508" spans="1:9">
       <c r="A508" s="3" t="s">
-        <v>1442</v>
+        <v>1432</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>1443</v>
+        <v>93</v>
       </c>
       <c r="C508" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D508" s="3" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="E508" s="3" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="F508" s="3"/>
       <c r="G508" s="3" t="s">
-        <v>1444</v>
+        <v>1433</v>
       </c>
       <c r="H508" s="3" t="s">
         <v>16</v>
@@ -18919,23 +18981,23 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" s="3" t="s">
-        <v>1445</v>
+        <v>1434</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1446</v>
+        <v>1435</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D509" s="3" t="s">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="E509" s="3" t="s">
-        <v>1447</v>
+        <v>1436</v>
       </c>
       <c r="F509" s="3"/>
       <c r="G509" s="3" t="s">
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="H509" s="3" t="s">
         <v>16</v>
@@ -18946,23 +19008,23 @@
     </row>
     <row r="510" spans="1:9">
       <c r="A510" s="3" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>1449</v>
+        <v>1439</v>
       </c>
       <c r="C510" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="E510" s="3" t="s">
-        <v>90</v>
+        <v>1440</v>
       </c>
       <c r="F510" s="3"/>
       <c r="G510" s="3" t="s">
-        <v>1450</v>
+        <v>1441</v>
       </c>
       <c r="H510" s="3" t="s">
         <v>16</v>
@@ -18973,23 +19035,23 @@
     </row>
     <row r="511" spans="1:9">
       <c r="A511" s="3" t="s">
-        <v>1451</v>
+        <v>1442</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1452</v>
+        <v>1443</v>
       </c>
       <c r="C511" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>99</v>
+        <v>347</v>
       </c>
       <c r="E511" s="3" t="s">
-        <v>123</v>
+        <v>348</v>
       </c>
       <c r="F511" s="3"/>
       <c r="G511" s="3" t="s">
-        <v>1453</v>
+        <v>1444</v>
       </c>
       <c r="H511" s="3" t="s">
         <v>16</v>
@@ -19000,23 +19062,23 @@
     </row>
     <row r="512" spans="1:9">
       <c r="A512" s="3" t="s">
-        <v>1454</v>
+        <v>1445</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>1455</v>
+        <v>1446</v>
       </c>
       <c r="C512" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E512" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F512" s="3"/>
       <c r="G512" s="3" t="s">
-        <v>1456</v>
+        <v>1447</v>
       </c>
       <c r="H512" s="3" t="s">
         <v>16</v>
@@ -19027,23 +19089,23 @@
     </row>
     <row r="513" spans="1:9">
       <c r="A513" s="3" t="s">
-        <v>1457</v>
+        <v>1448</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>1458</v>
+        <v>1449</v>
       </c>
       <c r="C513" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="E513" s="3" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="F513" s="3"/>
       <c r="G513" s="3" t="s">
-        <v>1459</v>
+        <v>1450</v>
       </c>
       <c r="H513" s="3" t="s">
         <v>16</v>
@@ -19054,23 +19116,23 @@
     </row>
     <row r="514" spans="1:9">
       <c r="A514" s="3" t="s">
-        <v>1460</v>
+        <v>1451</v>
       </c>
       <c r="B514" s="3" t="s">
-        <v>1461</v>
+        <v>1452</v>
       </c>
       <c r="C514" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="E514" s="3" t="s">
-        <v>1462</v>
+        <v>82</v>
       </c>
       <c r="F514" s="3"/>
       <c r="G514" s="3" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="H514" s="3" t="s">
         <v>16</v>
@@ -19081,10 +19143,10 @@
     </row>
     <row r="515" spans="1:9">
       <c r="A515" s="3" t="s">
-        <v>1463</v>
+        <v>1454</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>1464</v>
+        <v>1455</v>
       </c>
       <c r="C515" s="3" t="s">
         <v>24</v>
@@ -19097,7 +19159,7 @@
       </c>
       <c r="F515" s="3"/>
       <c r="G515" s="3" t="s">
-        <v>1465</v>
+        <v>1456</v>
       </c>
       <c r="H515" s="3" t="s">
         <v>16</v>
@@ -19108,23 +19170,23 @@
     </row>
     <row r="516" spans="1:9">
       <c r="A516" s="3" t="s">
-        <v>1466</v>
+        <v>1457</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>1467</v>
+        <v>1458</v>
       </c>
       <c r="C516" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D516" s="3" t="s">
-        <v>223</v>
+        <v>44</v>
       </c>
       <c r="E516" s="3" t="s">
-        <v>1468</v>
+        <v>49</v>
       </c>
       <c r="F516" s="3"/>
       <c r="G516" s="3" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
       <c r="H516" s="3" t="s">
         <v>16</v>
@@ -19135,23 +19197,23 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" s="3" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
       <c r="C517" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>347</v>
+        <v>99</v>
       </c>
       <c r="E517" s="3" t="s">
-        <v>348</v>
+        <v>123</v>
       </c>
       <c r="F517" s="3"/>
       <c r="G517" s="3" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
       <c r="H517" s="3" t="s">
         <v>16</v>
@@ -19162,10 +19224,10 @@
     </row>
     <row r="518" spans="1:9">
       <c r="A518" s="3" t="s">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
       <c r="C518" s="3" t="s">
         <v>24</v>
@@ -19174,11 +19236,11 @@
         <v>99</v>
       </c>
       <c r="E518" s="3" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F518" s="3"/>
       <c r="G518" s="3" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
       <c r="H518" s="3" t="s">
         <v>16</v>
@@ -19189,10 +19251,10 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" s="3" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
       <c r="C519" s="3" t="s">
         <v>24</v>
@@ -19201,11 +19263,11 @@
         <v>99</v>
       </c>
       <c r="E519" s="3" t="s">
-        <v>1462</v>
+        <v>123</v>
       </c>
       <c r="F519" s="3"/>
       <c r="G519" s="3" t="s">
-        <v>1478</v>
+        <v>1468</v>
       </c>
       <c r="H519" s="3" t="s">
         <v>16</v>
@@ -19216,23 +19278,23 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" s="3" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>1480</v>
+        <v>1470</v>
       </c>
       <c r="C520" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="E520" s="3" t="s">
-        <v>173</v>
+        <v>1471</v>
       </c>
       <c r="F520" s="3"/>
       <c r="G520" s="3" t="s">
-        <v>1481</v>
+        <v>1468</v>
       </c>
       <c r="H520" s="3" t="s">
         <v>16</v>
@@ -19243,23 +19305,23 @@
     </row>
     <row r="521" spans="1:9">
       <c r="A521" s="3" t="s">
-        <v>1482</v>
+        <v>1472</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
       <c r="C521" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>542</v>
+        <v>89</v>
       </c>
       <c r="E521" s="3" t="s">
-        <v>271</v>
+        <v>90</v>
       </c>
       <c r="F521" s="3"/>
       <c r="G521" s="3" t="s">
-        <v>1484</v>
+        <v>1474</v>
       </c>
       <c r="H521" s="3" t="s">
         <v>16</v>
@@ -19270,10 +19332,10 @@
     </row>
     <row r="522" spans="1:9">
       <c r="A522" s="3" t="s">
-        <v>1485</v>
+        <v>1475</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
       <c r="C522" s="3" t="s">
         <v>24</v>
@@ -19282,11 +19344,11 @@
         <v>99</v>
       </c>
       <c r="E522" s="3" t="s">
-        <v>325</v>
+        <v>123</v>
       </c>
       <c r="F522" s="3"/>
       <c r="G522" s="3" t="s">
-        <v>1487</v>
+        <v>1477</v>
       </c>
       <c r="H522" s="3" t="s">
         <v>16</v>
@@ -19297,23 +19359,23 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" s="3" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1489</v>
+        <v>1479</v>
       </c>
       <c r="C523" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E523" s="3" t="s">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="F523" s="3"/>
       <c r="G523" s="3" t="s">
-        <v>1490</v>
+        <v>1480</v>
       </c>
       <c r="H523" s="3" t="s">
         <v>16</v>
@@ -19324,23 +19386,23 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" s="3" t="s">
-        <v>1491</v>
+        <v>1481</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
       <c r="C524" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E524" s="3" t="s">
-        <v>267</v>
+        <v>123</v>
       </c>
       <c r="F524" s="3"/>
       <c r="G524" s="3" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
       <c r="H524" s="3" t="s">
         <v>16</v>
@@ -19351,23 +19413,23 @@
     </row>
     <row r="525" spans="1:9">
       <c r="A525" s="3" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="E525" s="3" t="s">
-        <v>1154</v>
+        <v>1486</v>
       </c>
       <c r="F525" s="3"/>
       <c r="G525" s="3" t="s">
-        <v>1496</v>
+        <v>1483</v>
       </c>
       <c r="H525" s="3" t="s">
         <v>16</v>
@@ -19378,23 +19440,23 @@
     </row>
     <row r="526" spans="1:9">
       <c r="A526" s="3" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
       <c r="C526" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D526" s="3" t="s">
-        <v>542</v>
+        <v>347</v>
       </c>
       <c r="E526" s="3" t="s">
-        <v>49</v>
+        <v>348</v>
       </c>
       <c r="F526" s="3"/>
       <c r="G526" s="3" t="s">
-        <v>1499</v>
+        <v>1489</v>
       </c>
       <c r="H526" s="3" t="s">
         <v>16</v>
@@ -19405,23 +19467,23 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" s="3" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>1501</v>
+        <v>1491</v>
       </c>
       <c r="C527" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>542</v>
+        <v>223</v>
       </c>
       <c r="E527" s="3" t="s">
-        <v>35</v>
+        <v>1492</v>
       </c>
       <c r="F527" s="3"/>
       <c r="G527" s="3" t="s">
-        <v>1502</v>
+        <v>1493</v>
       </c>
       <c r="H527" s="3" t="s">
         <v>16</v>
@@ -19432,23 +19494,23 @@
     </row>
     <row r="528" spans="1:9">
       <c r="A528" s="3" t="s">
-        <v>1503</v>
+        <v>1494</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>1504</v>
+        <v>1495</v>
       </c>
       <c r="C528" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>198</v>
+        <v>347</v>
       </c>
       <c r="E528" s="3" t="s">
-        <v>1505</v>
+        <v>348</v>
       </c>
       <c r="F528" s="3"/>
       <c r="G528" s="3" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
       <c r="H528" s="3" t="s">
         <v>16</v>
@@ -19459,23 +19521,23 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" s="3" t="s">
-        <v>1507</v>
+        <v>1497</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>1508</v>
+        <v>1498</v>
       </c>
       <c r="C529" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="E529" s="3" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="F529" s="3"/>
       <c r="G529" s="3" t="s">
-        <v>1509</v>
+        <v>1499</v>
       </c>
       <c r="H529" s="3" t="s">
         <v>16</v>
@@ -19486,23 +19548,23 @@
     </row>
     <row r="530" spans="1:9">
       <c r="A530" s="3" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="C530" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E530" s="3" t="s">
-        <v>116</v>
+        <v>1486</v>
       </c>
       <c r="F530" s="3"/>
       <c r="G530" s="3" t="s">
-        <v>1512</v>
+        <v>1502</v>
       </c>
       <c r="H530" s="3" t="s">
         <v>16</v>
@@ -19513,23 +19575,23 @@
     </row>
     <row r="531" spans="1:9">
       <c r="A531" s="3" t="s">
-        <v>1513</v>
+        <v>1503</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>200</v>
+        <v>1504</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D531" s="3" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E531" s="3" t="s">
-        <v>267</v>
+        <v>173</v>
       </c>
       <c r="F531" s="3"/>
       <c r="G531" s="3" t="s">
-        <v>1514</v>
+        <v>1505</v>
       </c>
       <c r="H531" s="3" t="s">
         <v>16</v>
@@ -19540,23 +19602,23 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" s="3" t="s">
-        <v>1515</v>
+        <v>1506</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>1516</v>
+        <v>1507</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D532" s="3" t="s">
-        <v>70</v>
+        <v>542</v>
       </c>
       <c r="E532" s="3" t="s">
-        <v>1517</v>
+        <v>271</v>
       </c>
       <c r="F532" s="3"/>
       <c r="G532" s="3" t="s">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="H532" s="3" t="s">
         <v>16</v>
@@ -19567,23 +19629,23 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" s="3" t="s">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="C533" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E533" s="3" t="s">
-        <v>35</v>
+        <v>325</v>
       </c>
       <c r="F533" s="3"/>
       <c r="G533" s="3" t="s">
-        <v>1521</v>
+        <v>1511</v>
       </c>
       <c r="H533" s="3" t="s">
         <v>16</v>
@@ -19594,23 +19656,23 @@
     </row>
     <row r="534" spans="1:9">
       <c r="A534" s="3" t="s">
-        <v>1522</v>
+        <v>1512</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D534" s="3" t="s">
-        <v>1524</v>
+        <v>70</v>
       </c>
       <c r="E534" s="3" t="s">
-        <v>1525</v>
+        <v>422</v>
       </c>
       <c r="F534" s="3"/>
       <c r="G534" s="3" t="s">
-        <v>1526</v>
+        <v>1514</v>
       </c>
       <c r="H534" s="3" t="s">
         <v>16</v>
@@ -19621,23 +19683,23 @@
     </row>
     <row r="535" spans="1:9">
       <c r="A535" s="3" t="s">
-        <v>1527</v>
+        <v>1515</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>1528</v>
+        <v>1516</v>
       </c>
       <c r="C535" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="E535" s="3" t="s">
-        <v>1529</v>
+        <v>267</v>
       </c>
       <c r="F535" s="3"/>
       <c r="G535" s="3" t="s">
-        <v>1530</v>
+        <v>1517</v>
       </c>
       <c r="H535" s="3" t="s">
         <v>16</v>
@@ -19648,23 +19710,23 @@
     </row>
     <row r="536" spans="1:9">
       <c r="A536" s="3" t="s">
-        <v>1531</v>
+        <v>1518</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>1532</v>
+        <v>1519</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D536" s="3" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="E536" s="3" t="s">
-        <v>1505</v>
+        <v>1167</v>
       </c>
       <c r="F536" s="3"/>
       <c r="G536" s="3" t="s">
-        <v>1533</v>
+        <v>1520</v>
       </c>
       <c r="H536" s="3" t="s">
         <v>16</v>
@@ -19675,23 +19737,23 @@
     </row>
     <row r="537" spans="1:9">
       <c r="A537" s="3" t="s">
-        <v>1534</v>
+        <v>1521</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>1535</v>
+        <v>1522</v>
       </c>
       <c r="C537" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>70</v>
+        <v>542</v>
       </c>
       <c r="E537" s="3" t="s">
-        <v>1536</v>
+        <v>49</v>
       </c>
       <c r="F537" s="3"/>
       <c r="G537" s="3" t="s">
-        <v>1537</v>
+        <v>1523</v>
       </c>
       <c r="H537" s="3" t="s">
         <v>16</v>
@@ -19702,23 +19764,23 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" s="3" t="s">
-        <v>1538</v>
+        <v>1524</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>1539</v>
+        <v>1525</v>
       </c>
       <c r="C538" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>99</v>
+        <v>542</v>
       </c>
       <c r="E538" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="F538" s="3"/>
       <c r="G538" s="3" t="s">
-        <v>1540</v>
+        <v>1526</v>
       </c>
       <c r="H538" s="3" t="s">
         <v>16</v>
@@ -19729,23 +19791,23 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" s="3" t="s">
-        <v>1541</v>
+        <v>1527</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1542</v>
+        <v>1528</v>
       </c>
       <c r="C539" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="E539" s="3" t="s">
-        <v>155</v>
+        <v>1529</v>
       </c>
       <c r="F539" s="3"/>
       <c r="G539" s="3" t="s">
-        <v>1543</v>
+        <v>1530</v>
       </c>
       <c r="H539" s="3" t="s">
         <v>16</v>
@@ -19756,10 +19818,10 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" s="3" t="s">
-        <v>1544</v>
+        <v>1531</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>742</v>
+        <v>1532</v>
       </c>
       <c r="C540" s="3" t="s">
         <v>24</v>
@@ -19772,7 +19834,7 @@
       </c>
       <c r="F540" s="3"/>
       <c r="G540" s="3" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
       <c r="H540" s="3" t="s">
         <v>16</v>
@@ -19783,10 +19845,10 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" s="3" t="s">
-        <v>1545</v>
+        <v>1534</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1546</v>
+        <v>1535</v>
       </c>
       <c r="C541" s="3" t="s">
         <v>24</v>
@@ -19795,11 +19857,11 @@
         <v>112</v>
       </c>
       <c r="E541" s="3" t="s">
-        <v>503</v>
+        <v>116</v>
       </c>
       <c r="F541" s="3"/>
       <c r="G541" s="3" t="s">
-        <v>1547</v>
+        <v>1536</v>
       </c>
       <c r="H541" s="3" t="s">
         <v>16</v>
@@ -19810,23 +19872,23 @@
     </row>
     <row r="542" spans="1:9">
       <c r="A542" s="3" t="s">
-        <v>1548</v>
+        <v>1537</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>1549</v>
+        <v>200</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="E542" s="3" t="s">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="F542" s="3"/>
       <c r="G542" s="3" t="s">
-        <v>1550</v>
+        <v>1538</v>
       </c>
       <c r="H542" s="3" t="s">
         <v>16</v>
@@ -19837,23 +19899,23 @@
     </row>
     <row r="543" spans="1:9">
       <c r="A543" s="3" t="s">
-        <v>1551</v>
+        <v>1539</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1552</v>
+        <v>1540</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="E543" s="3" t="s">
-        <v>35</v>
+        <v>1541</v>
       </c>
       <c r="F543" s="3"/>
       <c r="G543" s="3" t="s">
-        <v>1553</v>
+        <v>1542</v>
       </c>
       <c r="H543" s="3" t="s">
         <v>16</v>
@@ -19864,23 +19926,23 @@
     </row>
     <row r="544" spans="1:9">
       <c r="A544" s="3" t="s">
-        <v>1554</v>
+        <v>1543</v>
       </c>
       <c r="B544" s="3" t="s">
-        <v>1555</v>
+        <v>1544</v>
       </c>
       <c r="C544" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D544" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E544" s="3" t="s">
-        <v>390</v>
+        <v>35</v>
       </c>
       <c r="F544" s="3"/>
       <c r="G544" s="3" t="s">
-        <v>1556</v>
+        <v>1545</v>
       </c>
       <c r="H544" s="3" t="s">
         <v>16</v>
@@ -19891,23 +19953,23 @@
     </row>
     <row r="545" spans="1:9">
       <c r="A545" s="3" t="s">
-        <v>1557</v>
+        <v>1546</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>1558</v>
+        <v>1547</v>
       </c>
       <c r="C545" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>542</v>
+        <v>1548</v>
       </c>
       <c r="E545" s="3" t="s">
-        <v>49</v>
+        <v>1549</v>
       </c>
       <c r="F545" s="3"/>
       <c r="G545" s="3" t="s">
-        <v>1559</v>
+        <v>1550</v>
       </c>
       <c r="H545" s="3" t="s">
         <v>16</v>
@@ -19918,23 +19980,23 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" s="3" t="s">
-        <v>1560</v>
+        <v>1551</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>1561</v>
+        <v>1552</v>
       </c>
       <c r="C546" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="E546" s="3" t="s">
-        <v>108</v>
+        <v>1553</v>
       </c>
       <c r="F546" s="3"/>
       <c r="G546" s="3" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="H546" s="3" t="s">
         <v>16</v>
@@ -19945,23 +20007,23 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" s="3" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="C547" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="E547" s="3" t="s">
-        <v>90</v>
+        <v>1529</v>
       </c>
       <c r="F547" s="3"/>
       <c r="G547" s="3" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="H547" s="3" t="s">
         <v>16</v>
@@ -19972,23 +20034,23 @@
     </row>
     <row r="548" spans="1:9">
       <c r="A548" s="3" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="C548" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E548" s="3" t="s">
-        <v>90</v>
+        <v>1560</v>
       </c>
       <c r="F548" s="3"/>
       <c r="G548" s="3" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="H548" s="3" t="s">
         <v>16</v>
@@ -19999,10 +20061,10 @@
     </row>
     <row r="549" spans="1:9">
       <c r="A549" s="3" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="C549" s="3" t="s">
         <v>24</v>
@@ -20011,11 +20073,11 @@
         <v>99</v>
       </c>
       <c r="E549" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F549" s="3"/>
       <c r="G549" s="3" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="H549" s="3" t="s">
         <v>16</v>
@@ -20026,23 +20088,23 @@
     </row>
     <row r="550" spans="1:9">
       <c r="A550" s="3" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="B550" s="3" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="C550" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>1328</v>
+        <v>154</v>
       </c>
       <c r="E550" s="3" t="s">
-        <v>869</v>
+        <v>155</v>
       </c>
       <c r="F550" s="3"/>
       <c r="G550" s="3" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="H550" s="3" t="s">
         <v>16</v>
@@ -20053,23 +20115,23 @@
     </row>
     <row r="551" spans="1:9">
       <c r="A551" s="3" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1574</v>
+        <v>742</v>
       </c>
       <c r="C551" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E551" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F551" s="3"/>
       <c r="G551" s="3" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
       <c r="H551" s="3" t="s">
         <v>16</v>
@@ -20080,23 +20142,23 @@
     </row>
     <row r="552" spans="1:9">
       <c r="A552" s="3" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="C552" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="E552" s="3" t="s">
-        <v>90</v>
+        <v>503</v>
       </c>
       <c r="F552" s="3"/>
       <c r="G552" s="3" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="H552" s="3" t="s">
         <v>16</v>
@@ -20107,10 +20169,10 @@
     </row>
     <row r="553" spans="1:9">
       <c r="A553" s="3" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="C553" s="3" t="s">
         <v>24</v>
@@ -20119,11 +20181,11 @@
         <v>44</v>
       </c>
       <c r="E553" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F553" s="3"/>
       <c r="G553" s="3" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="H553" s="3" t="s">
         <v>16</v>
@@ -20134,23 +20196,23 @@
     </row>
     <row r="554" spans="1:9">
       <c r="A554" s="3" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="C554" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D554" s="3" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E554" s="3" t="s">
-        <v>1583</v>
+        <v>35</v>
       </c>
       <c r="F554" s="3"/>
       <c r="G554" s="3" t="s">
-        <v>1584</v>
+        <v>1577</v>
       </c>
       <c r="H554" s="3" t="s">
         <v>16</v>
@@ -20161,23 +20223,23 @@
     </row>
     <row r="555" spans="1:9">
       <c r="A555" s="3" t="s">
-        <v>1585</v>
+        <v>1578</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="C555" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="E555" s="3" t="s">
-        <v>237</v>
+        <v>390</v>
       </c>
       <c r="F555" s="3"/>
       <c r="G555" s="3" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="H555" s="3" t="s">
         <v>16</v>
@@ -20188,23 +20250,23 @@
     </row>
     <row r="556" spans="1:9">
       <c r="A556" s="3" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="C556" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="E556" s="3" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="F556" s="3"/>
       <c r="G556" s="3" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="H556" s="3" t="s">
         <v>16</v>
@@ -20215,23 +20277,23 @@
     </row>
     <row r="557" spans="1:9">
       <c r="A557" s="3" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="C557" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="E557" s="3" t="s">
-        <v>321</v>
+        <v>108</v>
       </c>
       <c r="F557" s="3"/>
       <c r="G557" s="3" t="s">
-        <v>1593</v>
+        <v>1583</v>
       </c>
       <c r="H557" s="3" t="s">
         <v>16</v>
@@ -20242,23 +20304,23 @@
     </row>
     <row r="558" spans="1:9">
       <c r="A558" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="C558" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E558" s="3" t="s">
-        <v>869</v>
+        <v>90</v>
       </c>
       <c r="F558" s="3"/>
       <c r="G558" s="3" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="H558" s="3" t="s">
         <v>16</v>
@@ -20269,23 +20331,23 @@
     </row>
     <row r="559" spans="1:9">
       <c r="A559" s="3" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="C559" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D559" s="3" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E559" s="3" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="F559" s="3"/>
       <c r="G559" s="3" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="H559" s="3" t="s">
         <v>16</v>
@@ -20296,23 +20358,23 @@
     </row>
     <row r="560" spans="1:9">
       <c r="A560" s="3" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="B560" s="3" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="C560" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E560" s="3" t="s">
-        <v>425</v>
+        <v>123</v>
       </c>
       <c r="F560" s="3"/>
       <c r="G560" s="3" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="H560" s="3" t="s">
         <v>16</v>
@@ -20323,28 +20385,325 @@
     </row>
     <row r="561" spans="1:9">
       <c r="A561" s="3" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="C561" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D561" s="3" t="s">
-        <v>39</v>
+        <v>1352</v>
       </c>
       <c r="E561" s="3" t="s">
-        <v>177</v>
+        <v>873</v>
       </c>
       <c r="F561" s="3"/>
       <c r="G561" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="H561" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I561" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="562" spans="1:9">
+      <c r="A562" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B562" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D562" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E562" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F562" s="3"/>
+      <c r="G562" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="H562" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I562" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="563" spans="1:9">
+      <c r="A563" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D563" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E563" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F563" s="3"/>
+      <c r="G563" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H563" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I563" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="564" spans="1:9">
+      <c r="A564" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D564" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E564" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F564" s="3"/>
+      <c r="G564" s="3" t="s">
         <v>1604</v>
       </c>
-      <c r="H561" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I561" s="3" t="s">
+      <c r="H564" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I564" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="565" spans="1:9">
+      <c r="A565" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B565" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D565" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E565" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F565" s="3"/>
+      <c r="G565" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H565" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I565" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="566" spans="1:9">
+      <c r="A566" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B566" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D566" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E566" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F566" s="3"/>
+      <c r="G566" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H566" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I566" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="567" spans="1:9">
+      <c r="A567" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D567" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E567" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F567" s="3"/>
+      <c r="G567" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H567" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I567" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="568" spans="1:9">
+      <c r="A568" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B568" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D568" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E568" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F568" s="3"/>
+      <c r="G568" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H568" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I568" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="569" spans="1:9">
+      <c r="A569" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D569" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E569" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="F569" s="3"/>
+      <c r="G569" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H569" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I569" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="570" spans="1:9">
+      <c r="A570" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B570" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D570" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E570" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F570" s="3"/>
+      <c r="G570" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H570" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I570" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="571" spans="1:9">
+      <c r="A571" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D571" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E571" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F571" s="3"/>
+      <c r="G571" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H571" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I571" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="572" spans="1:9">
+      <c r="A572" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B572" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D572" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E572" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F572" s="3"/>
+      <c r="G572" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H572" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I572" s="3" t="s">
         <v>17</v>
       </c>
     </row>
